--- a/config/auto_configs/2015_Hyundai_Hyundai_Veloster(FS)_G 1.6 T-GDI.xlsx
+++ b/config/auto_configs/2015_Hyundai_Hyundai_Veloster(FS)_G 1.6 T-GDI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HMA_00024</t>
+          <t>HMA_00232</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B1678</t>
+          <t>P0006</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -542,17 +542,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HMA_00022</t>
+          <t>HMA_00232</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>P0007</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -564,20 +564,1186 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>P0051</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>P0052</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>P0057</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>P0058</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>P0101</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>P0102</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>P0103</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>P0105</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>P0339</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>P0340</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>P0600</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>P061B</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>P0638</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>P0660</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>P0661</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>P0662</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>P0820</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>P1111</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>P1230</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>P1505</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>P1506</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>P1507</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>P1508</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>P1602</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>P1691</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>P1692</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>P1780</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>P2232</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>P2270</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>P2271</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>P2272</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>P2273</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>P2501</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>P2502</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>P2503</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>U0122</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HMA_00232</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>U0164</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HMA_00021</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>P0705</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HMA_00021</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>U0001</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HMA_00021</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>U0100</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HMA_00022</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>SRS</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>HMA_00023</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>B1678</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>HMA_00024</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>B1678</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>TPMS</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>HMA_0023C</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HMA_00234</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BCM</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HMA_00238</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CLU</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HMA_0023A</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HMA_003A8</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>IMM</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HMA_00052</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ODS</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HMA_0023E</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HMA_0023B</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HMA_002DC</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>T-CS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HMA_0023D</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>TMU</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>HMA_00054</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>00</t>
         </is>
